--- a/artfynd/A 34147-2022 artfynd.xlsx
+++ b/artfynd/A 34147-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34147-2022 artfynd.xlsx
+++ b/artfynd/A 34147-2022 artfynd.xlsx
@@ -1168,7 +1168,7 @@
         <v>118569709</v>
       </c>
       <c r="B6" t="n">
-        <v>90522</v>
+        <v>90529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 34147-2022 artfynd.xlsx
+++ b/artfynd/A 34147-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>59615173</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624370.7419921524</v>
+        <v>624371</v>
       </c>
       <c r="R2" t="n">
-        <v>6634853.379763233</v>
+        <v>6634853</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,19 +753,9 @@
           <t>2016-05-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-05-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,56 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101782531</v>
+        <v>103688530</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>4189</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ramsjön, S, Upl</t>
+          <t>Ramsjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624170.587351363</v>
+        <v>624181</v>
       </c>
       <c r="R3" t="n">
-        <v>6634885.922716233</v>
+        <v>6634889</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-03-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-03-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,84 +866,81 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Eva Allestedt</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Annika Norin, Björn Bråvander, Didrik Vanhoenacker, Karin Wiklund, Lars Gerre, Maria Brandt, Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SMF:s mykologivecka</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103688530</v>
+        <v>61906889</v>
       </c>
       <c r="B4" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6056</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4189</v>
+        <v>105990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Matt starrbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Plateumaris rustica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Kunze, 1818)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramsjön, Upl</t>
+          <t>Ramsjön SV, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624181.5612268356</v>
+        <v>624104</v>
       </c>
       <c r="R4" t="n">
-        <v>6634889.308365758</v>
+        <v>6635008</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,22 +967,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-06-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hittades både på vasstarr och på blåsstarr</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,69 +989,102 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>blött, halvskuggigt kärr med glesa alar, lös botten, tuvad hundstarr, vasstarr, blåsstarr, vattenklöver, fräken</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Carex acuta, Carex vesicaria</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Carex acuta, Carex vesicaria</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Håkan Ljungberg</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Håkan Ljungberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Norin, Björn Bråvander, Didrik Vanhoenacker, Karin Wiklund, Lars Gerre, Maria Brandt, Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Håkan Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103688549</v>
+        <v>118569044</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>208245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ramsjön, Upl</t>
+          <t>Ramsjön, S, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624169.5805579491</v>
+        <v>624361</v>
       </c>
       <c r="R5" t="n">
-        <v>6634885.889044927</v>
+        <v>6634908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,22 +1111,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,75 +1125,85 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Annika Norin, Björn Bråvander, Didrik Vanhoenacker, Karin Wiklund, Lars Gerre, Maria Brandt, Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SMF:s mykologivecka</t>
-        </is>
-      </c>
+          <t>Björn Bråvander, Carina Lerdahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118569709</v>
+        <v>118569028</v>
       </c>
       <c r="B6" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ramsjön, S, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624167</v>
+        <v>624361</v>
       </c>
       <c r="R6" t="n">
-        <v>6634890</v>
+        <v>6634908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,26 +1248,6 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Levande stående gran på stammen</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande stående gran på stammen</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1288,6 +1260,108 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>101782376</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ramsjön, S, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>624393</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6634835</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-03-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-03-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Björn Bråvander, Eva Allestedt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
